--- a/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:22:20+00:00</t>
+    <t>2026-09-04T10:10:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:10:30+00:00</t>
+    <t>2026-09-04T12:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:54:27+00:00</t>
+    <t>2026-09-07T07:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-TRE-R222-MediaTypeCorpsCDANonStructure-all.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:40:03+00:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
